--- a/ig/nr-impr-organization-system/StructureDefinition-as-ext-healthcareservice-authorization-number-arhgos.xlsx
+++ b/ig/nr-impr-organization-system/StructureDefinition-as-ext-healthcareservice-authorization-number-arhgos.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-07-05T15:48:53+00:00</t>
+    <t>2023-07-05T15:49:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-impr-organization-system/StructureDefinition-as-ext-healthcareservice-authorization-number-arhgos.xlsx
+++ b/ig/nr-impr-organization-system/StructureDefinition-as-ext-healthcareservice-authorization-number-arhgos.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-07-05T15:49:30+00:00</t>
+    <t>2023-07-05T16:18:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-impr-organization-system/StructureDefinition-as-ext-healthcareservice-authorization-number-arhgos.xlsx
+++ b/ig/nr-impr-organization-system/StructureDefinition-as-ext-healthcareservice-authorization-number-arhgos.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-07-05T16:18:59+00:00</t>
+    <t>2023-07-08T08:21:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-impr-organization-system/StructureDefinition-as-ext-healthcareservice-authorization-number-arhgos.xlsx
+++ b/ig/nr-impr-organization-system/StructureDefinition-as-ext-healthcareservice-authorization-number-arhgos.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-07-08T08:21:48+00:00</t>
+    <t>2023-07-10T15:55:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
